--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T06:35:39+00:00</t>
+    <t>2026-03-30T12:50:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:32:58+00:00</t>
+    <t>2026-04-02T10:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:59:26+00:00</t>
+    <t>2026-04-02T12:19:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T07:54:58+00:00</t>
+    <t>2026-04-13T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:15:24+00:00</t>
+    <t>2026-04-14T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
